--- a/data/gravel/Curve Big Kev 2025.xlsx
+++ b/data/gravel/Curve Big Kev 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF452A07-60D5-4846-B44C-073FE1EA09B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1800263E-CCE4-D444-92F6-8C0C36B7FAF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="3820" windowWidth="23540" windowHeight="14180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="118">
   <si>
     <t>brand</t>
   </si>
@@ -359,9 +359,6 @@
     <t>threaded 85.5</t>
   </si>
   <si>
-    <t>https://www.curvecycling.com/products/big-kev-titanium-frameset</t>
-  </si>
-  <si>
     <t>Big Kev</t>
   </si>
   <si>
@@ -384,6 +381,12 @@
   </si>
   <si>
     <t>a8:j36</t>
+  </si>
+  <si>
+    <t>https://www.curvecycling.com/cdn/shop/products/IMG_4331-Edit.jpg?v=1756175673</t>
+  </si>
+  <si>
+    <t>https://www.curvecycling.com/products/big-kev</t>
   </si>
 </sst>
 </file>
@@ -743,7 +746,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -767,7 +770,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -775,7 +783,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -798,7 +806,7 @@
         <v>83</v>
       </c>
       <c r="G8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H8" t="s">
         <v>84</v>
@@ -1039,7 +1047,7 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C16">
         <v>1009</v>
@@ -1071,7 +1079,7 @@
         <v>102</v>
       </c>
       <c r="B17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C17">
         <v>1004</v>
@@ -1231,7 +1239,7 @@
         <v>103</v>
       </c>
       <c r="B22" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C22">
         <v>581</v>
@@ -1391,7 +1399,7 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C26">
         <v>72</v>
@@ -1423,7 +1431,7 @@
         <v>104</v>
       </c>
       <c r="B27" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C27">
         <v>79</v>

--- a/data/gravel/Curve Big Kev 2025.xlsx
+++ b/data/gravel/Curve Big Kev 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1800263E-CCE4-D444-92F6-8C0C36B7FAF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABD41FC2-230D-C441-8B91-983BD90ED531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="3820" windowWidth="23540" windowHeight="14180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="120">
   <si>
     <t>brand</t>
   </si>
@@ -387,6 +387,12 @@
   </si>
   <si>
     <t>https://www.curvecycling.com/products/big-kev</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Melbourne, Australia</t>
   </si>
 </sst>
 </file>
@@ -726,7 +732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R76"/>
+  <dimension ref="A1:R77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1911,6 +1917,14 @@
         <v>78</v>
       </c>
     </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>118</v>
+      </c>
+      <c r="B77" t="s">
+        <v>119</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Curve Big Kev 2025.xlsx
+++ b/data/gravel/Curve Big Kev 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABD41FC2-230D-C441-8B91-983BD90ED531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A39B6BC3-0E80-284B-A59A-350A1DD8615F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="3820" windowWidth="23540" windowHeight="14180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="126">
   <si>
     <t>brand</t>
   </si>
@@ -393,6 +393,24 @@
   </si>
   <si>
     <t>Melbourne, Australia</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -732,7 +750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R77"/>
+  <dimension ref="A1:R83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1742,186 +1760,216 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>46</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>47</v>
+        <v>121</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>48</v>
-      </c>
-      <c r="B55">
-        <v>27.2</v>
+        <v>122</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>49</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>76</v>
+        <v>123</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>50</v>
-      </c>
-      <c r="B57">
-        <v>40</v>
+        <v>124</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>51</v>
-      </c>
-      <c r="B58">
-        <v>48</v>
+        <v>125</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>52</v>
-      </c>
-      <c r="B59">
-        <v>180</v>
+        <v>46</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>53</v>
-      </c>
-      <c r="B60">
-        <v>160</v>
+        <v>47</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>54</v>
+        <v>48</v>
+      </c>
+      <c r="B61">
+        <v>27.2</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>106</v>
+        <v>76</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>56</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>77</v>
+        <v>50</v>
+      </c>
+      <c r="B63">
+        <v>40</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>57</v>
+        <v>51</v>
+      </c>
+      <c r="B64">
+        <v>48</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>58</v>
+        <v>52</v>
+      </c>
+      <c r="B65">
+        <v>180</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B66">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>60</v>
-      </c>
-      <c r="B67">
-        <v>1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>61</v>
-      </c>
-      <c r="B68">
-        <v>1</v>
+        <v>55</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>62</v>
-      </c>
-      <c r="B69">
-        <v>3</v>
+        <v>56</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>63</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>64</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>65</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>76</v>
+        <v>59</v>
+      </c>
+      <c r="B72">
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B73">
-        <v>2877</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B74">
-        <v>6060</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>68</v>
+        <v>62</v>
+      </c>
+      <c r="B75">
+        <v>3</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
+        <v>64</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>65</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>66</v>
+      </c>
+      <c r="B79">
+        <v>2877</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>67</v>
+      </c>
+      <c r="B80">
+        <v>6060</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>69</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
         <v>118</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B83" t="s">
         <v>119</v>
       </c>
     </row>
